--- a/docs/TEST-CASES.xlsx
+++ b/docs/TEST-CASES.xlsx
@@ -31,7 +31,7 @@
     <t>Expected result</t>
   </si>
   <si>
-    <t>เทคนิค / เหตุผล</t>
+    <t>Technique / Reason</t>
   </si>
   <si>
     <t>TC01</t>
@@ -52,7 +52,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>ค่าปกติ (จำนวนบวก)</t>
+    <t>Normal value (positive numbers)</t>
   </si>
   <si>
     <t>TC02</t>
@@ -67,7 +67,7 @@
     <t>-12</t>
   </si>
   <si>
-    <t>ค่าปกติ (จำนวนลบทั้งคู่)</t>
+    <t>Normal value (both negative)</t>
   </si>
   <si>
     <t>TC03</t>
@@ -82,7 +82,7 @@
     <t>-6</t>
   </si>
   <si>
-    <t>ค่าปกติ (บวกกับลบ)</t>
+    <t>Normal value (positive and negative)</t>
   </si>
   <si>
     <t>TC04</t>
@@ -91,7 +91,7 @@
     <t>0</t>
   </si>
   <si>
-    <t>ศูนย์</t>
+    <t>Zero</t>
   </si>
   <si>
     <t>TC05</t>
@@ -106,7 +106,7 @@
     <t>3.75</t>
   </si>
   <si>
-    <t>ทศนิยม</t>
+    <t>Decimals</t>
   </si>
   <si>
     <t>TC06</t>
@@ -121,16 +121,16 @@
     <t>10000000000</t>
   </si>
   <si>
-    <t>ขอบเขต: ช่องรับได้สูงสุด 10 หลัก, ผลลัพธ์ยาวเกิน 10 หลัก</t>
+    <t>Boundary: 10-digit input limit, result longer than 10 digits</t>
   </si>
   <si>
     <t>TC07</t>
   </si>
   <si>
-    <t>(ว่าง)</t>
-  </si>
-  <si>
-    <t>กรณีพิเศษ: ช่องว่างทั้งคู่ ระบบถือเป็น 0 (สมมติฐาน ต้องยืนยันกับ PO)</t>
+    <t>(empty)</t>
+  </si>
+  <si>
+    <t>Special case: two empty fields count as 0 (assumption, confirm with PO)</t>
   </si>
   <si>
     <t>TC08</t>
@@ -142,7 +142,7 @@
     <t>1001</t>
   </si>
   <si>
-    <t>กรณีพิเศษ: รูปแบบ scientific notation</t>
+    <t>Special case: scientific notation</t>
   </si>
   <si>
     <t>TC09</t>
@@ -151,7 +151,7 @@
     <t>Subtract</t>
   </si>
   <si>
-    <t>ค่าปกติ</t>
+    <t>Normal value</t>
   </si>
   <si>
     <t>TC10</t>
@@ -160,7 +160,7 @@
     <t>-2</t>
   </si>
   <si>
-    <t>ลำดับ operand: ผลติดลบ (จับบั๊กสลับช่อง)</t>
+    <t>Operand order: negative result (catches swapped fields)</t>
   </si>
   <si>
     <t>TC11</t>
@@ -169,7 +169,7 @@
     <t>-4</t>
   </si>
   <si>
-    <t>จำนวนลบลบด้วยจำนวนลบ</t>
+    <t>Negative minus negative</t>
   </si>
   <si>
     <t>TC12</t>
@@ -193,7 +193,7 @@
     <t>-9</t>
   </si>
   <si>
-    <t>ศูนย์เป็นตัวตั้ง</t>
+    <t>Zero as the first number</t>
   </si>
   <si>
     <t>TC14</t>
@@ -217,7 +217,7 @@
     <t>-18</t>
   </si>
   <si>
-    <t>ลบคูณบวก</t>
+    <t>Negative times positive</t>
   </si>
   <si>
     <t>TC16</t>
@@ -226,7 +226,7 @@
     <t>12</t>
   </si>
   <si>
-    <t>ลบคูณลบ</t>
+    <t>Negative times negative</t>
   </si>
   <si>
     <t>TC17</t>
@@ -235,7 +235,7 @@
     <t>123</t>
   </si>
   <si>
-    <t>คูณศูนย์</t>
+    <t>Multiply by zero</t>
   </si>
   <si>
     <t>TC18</t>
@@ -244,7 +244,7 @@
     <t>10</t>
   </si>
   <si>
-    <t>ทศนิยม ผลเป็นจำนวนเต็ม</t>
+    <t>Decimal with a whole-number result</t>
   </si>
   <si>
     <t>TC19</t>
@@ -256,7 +256,7 @@
     <t>9999800001</t>
   </si>
   <si>
-    <t>ขอบเขต: ผลลัพธ์ขนาดใหญ่ 10 หลัก</t>
+    <t>Boundary: large 10-digit result</t>
   </si>
   <si>
     <t>TC20</t>
@@ -274,19 +274,19 @@
     <t>3.5</t>
   </si>
   <si>
-    <t>ผลเป็นทศนิยม</t>
+    <t>Decimal result</t>
   </si>
   <si>
     <t>TC22</t>
   </si>
   <si>
-    <t>จำนวนลบ</t>
+    <t>Negative number</t>
   </si>
   <si>
     <t>TC23</t>
   </si>
   <si>
-    <t>ศูนย์หารด้วยจำนวน</t>
+    <t>Zero divided by a number</t>
   </si>
   <si>
     <t>TC24</t>
@@ -295,7 +295,7 @@
     <t>0.25</t>
   </si>
   <si>
-    <t>ลำดับ operand (ถ้าสลับจะได้ 4)</t>
+    <t>Operand order (swapped fields would give 4)</t>
   </si>
   <si>
     <t>TC25</t>
@@ -304,7 +304,7 @@
     <t>Error: Divide by zero error!</t>
   </si>
   <si>
-    <t>กรณีพิเศษ: หารด้วยศูนย์ ต้องแจ้ง error</t>
+    <t>Special case: divide by zero must show an error</t>
   </si>
   <si>
     <t>TC26</t>
@@ -316,7 +316,7 @@
     <t>23</t>
   </si>
   <si>
-    <t>ค่าปกติ: ต่อข้อความ ไม่ใช่บวกเลข</t>
+    <t>Normal value: joins text, does not add</t>
   </si>
   <si>
     <t>TC27</t>
@@ -331,7 +331,7 @@
     <t>abcdef</t>
   </si>
   <si>
-    <t>ตัวอักษรต้องใช้ได้ ไม่ต้อง validate ตัวเลข</t>
+    <t>Letters are allowed, no number check</t>
   </si>
   <si>
     <t>TC28</t>
@@ -346,13 +346,13 @@
     <t>-10.5</t>
   </si>
   <si>
-    <t>เครื่องหมายลบและทศนิยมถูกต่อเป็นข้อความ</t>
+    <t>Minus sign and decimal point are joined as text</t>
   </si>
   <si>
     <t>TC29</t>
   </si>
   <si>
-    <t>กรณีพิเศษ: ช่องแรกว่าง</t>
+    <t>Special case: first field empty</t>
   </si>
   <si>
     <t>TC30</t>
@@ -361,13 +361,13 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>Integers only: ตัดทศนิยมทิ้ง (3.75 → 3 ไม่ปัดขึ้น)</t>
+    <t>Integers only: drops the decimals (3.75 → 3, no rounding up)</t>
   </si>
   <si>
     <t>TC31</t>
   </si>
   <si>
-    <t>Integers only: ผลเป็นจำนวนเต็มอยู่แล้ว ไม่เปลี่ยน</t>
+    <t>Integers only: whole-number result is unchanged</t>
   </si>
   <si>
     <t>TC32</t>
@@ -385,7 +385,7 @@
     <t>TC34</t>
   </si>
   <si>
-    <t>Integers only กับค่าลบ: ตัดเข้าหาศูนย์ (-3.5 → -3)</t>
+    <t>Integers only with a negative result: truncates toward zero (-3.5 → -3)</t>
   </si>
   <si>
     <t>TC35</t>
@@ -394,7 +394,7 @@
     <t>0.4</t>
   </si>
   <si>
-    <t>Integers only: ผลน้อยกว่า 1 (0.8 → 0)</t>
+    <t>Integers only: result below 1 (0.8 → 0)</t>
   </si>
   <si>
     <t>TC36</t>
@@ -403,7 +403,7 @@
     <t>Error: Number 1 is not a number</t>
   </si>
   <si>
-    <t>Negative: ช่องแรกเป็นตัวอักษร</t>
+    <t>Negative: letters in First number</t>
   </si>
   <si>
     <t>TC37</t>
@@ -412,7 +412,7 @@
     <t>Error: Number 2 is not a number</t>
   </si>
   <si>
-    <t>Negative: ช่องที่สองเป็นตัวอักษร</t>
+    <t>Negative: letters in Second number</t>
   </si>
   <si>
     <t>TC38</t>
@@ -421,7 +421,7 @@
     <t>1,000</t>
   </si>
   <si>
-    <t>Negative: มีเครื่องหมายคั่นหลักพัน</t>
+    <t>Negative: thousands separator</t>
   </si>
   <si>
     <t>TC39</t>
@@ -430,7 +430,7 @@
     <t>2x</t>
   </si>
   <si>
-    <t>Negative: ตัวเลขปนตัวอักษร</t>
+    <t>Negative: digits mixed with letters</t>
   </si>
   <si>
     <t>TC40</t>
@@ -439,7 +439,7 @@
     <t>!@#</t>
   </si>
   <si>
-    <t>Negative: อักขระพิเศษ</t>
+    <t>Negative: special characters</t>
   </si>
   <si>
     <t>TC41</t>
@@ -448,19 +448,19 @@
     <t>Add + Clear</t>
   </si>
   <si>
-    <t>ปุ่ม Clear: คำนวณแล้วกด Clear ช่อง Answer ต้องว่าง</t>
+    <t>Clear: Answer is empty after a calculation</t>
   </si>
   <si>
     <t>TC42</t>
   </si>
   <si>
-    <t>ปุ่ม Clear: ใช้กับ Integers only แล้วกด Clear ช่อง Answer ต้องว่าง</t>
+    <t>Clear with Integers only ticked: Answer is empty</t>
   </si>
   <si>
     <t>TC43</t>
   </si>
   <si>
-    <t>ปุ่ม Clear หลัง error: ข้อความ error และ Answer ต้องว่าง</t>
+    <t>Clear after an error: error message and Answer are empty</t>
   </si>
   <si>
     <t>TC44</t>
@@ -469,7 +469,7 @@
     <t>Clear</t>
   </si>
   <si>
-    <t>ปุ่ม Clear: กดได้ทันทีที่เปิดหน้า ก่อนคำนวณครั้งแรก</t>
+    <t>Clear: button works right after page load, before any calculation</t>
   </si>
 </sst>
 </file>
@@ -488,11 +488,11 @@
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="10"/>
-      <name val="Tahoma"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Tahoma"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1929,6 +1929,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
